--- a/management_forms/007_finance_task_assignment_form--management_forms.xlsx
+++ b/management_forms/007_finance_task_assignment_form--management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'finance_manager',_'value':_'finance_manager'}</t>
+          <t>finance_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'finance_manager', 'value': 'finance_manager'}</t>
+          <t>finance manager</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'accounting_team',_'value':_'accounting_team'}</t>
+          <t>accounting_team</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'accounting_team', 'value': 'accounting_team'}</t>
+          <t>accounting team</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'high', 'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'medium', 'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'low', 'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'assigned',_'value':_'assigned'}</t>
+          <t>assigned</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'assigned', 'value': 'assigned'}</t>
+          <t>assigned</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'completed', 'value': 'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'finance_manager',_'value':_'finance_manager'}</t>
+          <t>finance_manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'finance_manager', 'value': 'finance_manager'}</t>
+          <t>finance manager</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'accounting_team',_'value':_'accounting_team'}</t>
+          <t>accounting_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'accounting_team', 'value': 'accounting_team'}</t>
+          <t>accounting team</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'accounting',_'value':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'accounting', 'value': 'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'reporting',_'value':_'reporting'}</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'reporting', 'value': 'reporting'}</t>
+          <t>reporting</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'finance',_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'finance', 'value': 'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
     </row>
